--- a/simulated_data/dyads_simulated/cond3_no_coupling/HRV_B.xlsx
+++ b/simulated_data/dyads_simulated/cond3_no_coupling/HRV_B.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A697"/>
+  <dimension ref="A1:A621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,3477 +430,3097 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>599.4824010561942</v>
+        <v>770.3783539461324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>623.3089874945389</v>
+        <v>720.8737877228697</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>680.9179424308558</v>
+        <v>672.452422693035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>660.6130746261316</v>
+        <v>694.1262560367853</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>679.3220514148079</v>
+        <v>631.5790355379214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>648.8583802211854</v>
+        <v>683.4720885287355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>660.9107202707252</v>
+        <v>653.6538429691464</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>667.4132640016079</v>
+        <v>737.5539982764057</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>681.1027686608658</v>
+        <v>750.2084533903277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>694.4987734887737</v>
+        <v>766.2852503355974</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>653.9626663455235</v>
+        <v>708.7517037568532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>615.3415229209171</v>
+        <v>679.1034307284169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>664.468886723184</v>
+        <v>680.1350012891412</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>709.8809932304686</v>
+        <v>688.8687149780566</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>671.1636816761306</v>
+        <v>683.3416029472144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>722.3053974362958</v>
+        <v>689.2269485954649</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>671.8091899460745</v>
+        <v>674.013763943103</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>600.9951880038784</v>
+        <v>721.5802446399664</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>630.4180878968673</v>
+        <v>727.6518745996459</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>633.078023019463</v>
+        <v>682.3599810166652</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>603.7578668898256</v>
+        <v>719.4307787555747</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>632.6169310114267</v>
+        <v>701.8749217667946</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>669.8797815171922</v>
+        <v>663.5835305912714</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>668.3615968179257</v>
+        <v>636.0481371369566</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>755.5106070318977</v>
+        <v>669.5703979354555</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>852.9457843506343</v>
+        <v>697.5174495319152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>894.9894669260275</v>
+        <v>720.2014597247235</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>849.098101658587</v>
+        <v>742.536858168549</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>719.5424210070555</v>
+        <v>703.294805557146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>607.4209245004276</v>
+        <v>723.2938501115278</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>561.0661198287125</v>
+        <v>765.2809992036466</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>576.6569082414748</v>
+        <v>769.2825120654377</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>574.5822356038808</v>
+        <v>769.621512853945</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>554.9257702848287</v>
+        <v>784.4683434657007</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>574.0137952884936</v>
+        <v>805.2811007716479</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>632.8639060031485</v>
+        <v>785.2329519801131</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>703.5673124059194</v>
+        <v>763.3300228881303</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>694.5245395380795</v>
+        <v>676.4859752209098</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>681.6911957324799</v>
+        <v>664.8133247617061</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>729.9894781446988</v>
+        <v>635.6409434901807</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>757.1721734986347</v>
+        <v>669.9364323782397</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>759.9372167688614</v>
+        <v>737.8874870335962</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>714.1699222074642</v>
+        <v>747.8439294168525</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>708.577906817311</v>
+        <v>815.0924474381113</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>709.3516277105465</v>
+        <v>753.9685947365519</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>758.4299389743272</v>
+        <v>678.7012318493807</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>776.0737669181203</v>
+        <v>693.7445606710497</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>750.9377228888354</v>
+        <v>707.1267114086623</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>753.252331238329</v>
+        <v>710.5979988445199</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>667.9670657191394</v>
+        <v>730.7117278955318</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>691.9200716907667</v>
+        <v>760.3326503663226</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>737.409402399642</v>
+        <v>733.6313225147321</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>746.4653854849885</v>
+        <v>744.0331479758981</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>700.4290594859697</v>
+        <v>701.2661799328228</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>679.6521978011256</v>
+        <v>673.8846217539987</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>678.8676399902229</v>
+        <v>657.7960241887126</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>649.3704650136963</v>
+        <v>670.4824495482101</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>623.8430595409384</v>
+        <v>745.267516743084</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>618.9096107166137</v>
+        <v>702.4625455686078</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>697.3452210623564</v>
+        <v>711.0533319662125</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>739.637999336793</v>
+        <v>716.8787929306006</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>680.7229382069124</v>
+        <v>680.0829108833284</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>686.697489515062</v>
+        <v>687.8942135307824</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>670.3784006100832</v>
+        <v>687.96239179904</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>771.0572283108519</v>
+        <v>716.5227053726469</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>787.1950578825846</v>
+        <v>703.990643154036</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>746.2635567900691</v>
+        <v>679.6222708396228</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>749.6192804561872</v>
+        <v>694.3276201130643</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>728.4506108036553</v>
+        <v>702.9586714751802</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>722.3762816234256</v>
+        <v>706.4568115730765</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>638.0081654786025</v>
+        <v>740.6375235717562</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>623.2715210181468</v>
+        <v>728.1985668208506</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>659.9090357784476</v>
+        <v>778.6371685307216</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>681.4052186249313</v>
+        <v>755.5780421117646</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>612.2287776389967</v>
+        <v>707.7717242536323</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>573.1920059634774</v>
+        <v>744.9944064614228</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>595.467146233787</v>
+        <v>789.1807357775704</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>658.3894191987412</v>
+        <v>829.936416975876</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>650.2709626087011</v>
+        <v>774.3033815280285</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>679.5327128028816</v>
+        <v>741.4431306291647</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>716.8725149576716</v>
+        <v>674.926652133891</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>734.1209335808046</v>
+        <v>662.1086557528954</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>747.5334874944224</v>
+        <v>655.4853271404611</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>737.6235635981061</v>
+        <v>664.9282692878842</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>647.6522299993164</v>
+        <v>698.4808893198463</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>568.9329093286303</v>
+        <v>771.2677308272121</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>531.1202191223786</v>
+        <v>751.4442549852589</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>524.5621422180093</v>
+        <v>708.0722483256636</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>537.4935050417448</v>
+        <v>671.0883585956964</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>570.1372085108644</v>
+        <v>661.9466636392203</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>595.2002315837746</v>
+        <v>668.0376816638898</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>578.2382390789564</v>
+        <v>664.7767676123948</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>553.3233656772652</v>
+        <v>660.6090549159944</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>568.6721051606014</v>
+        <v>708.0571545679533</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>649.7857546896597</v>
+        <v>782.6710775045171</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>703.4462273436829</v>
+        <v>818.3919389525158</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>717.9479598248264</v>
+        <v>816.3759348098125</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>692.0076178761008</v>
+        <v>823.9815416148843</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>735.7483675356917</v>
+        <v>795.4548459276225</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>697.7663772617291</v>
+        <v>724.089102435272</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>649.1066145164979</v>
+        <v>667.0475109525711</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>570.16025625704</v>
+        <v>666.0904910296779</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>564.6658717110284</v>
+        <v>673.0905228252055</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>575.1028186845275</v>
+        <v>671.7010918381021</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>595.0940491375434</v>
+        <v>685.7295439524478</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>556.7940419657305</v>
+        <v>724.7371680281987</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>506.9565408851844</v>
+        <v>791.0436865140582</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>555.0494816064599</v>
+        <v>775.4361587199838</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>578.5023706264383</v>
+        <v>715.9463863290227</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>608.2910869374416</v>
+        <v>647.0639075881763</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>636.0761310598519</v>
+        <v>606.3588981690771</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>639.9273841406767</v>
+        <v>541.5116607639732</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>665.1039523161728</v>
+        <v>517.9737840692269</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>656.9032289000205</v>
+        <v>541.8651590646562</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>635.09566733903</v>
+        <v>541.8002265303699</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>632.9589492908809</v>
+        <v>549.8945360553193</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>643.1485477410916</v>
+        <v>633.3198859543216</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>763.7404733275446</v>
+        <v>635.3338232113686</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>828.2342179043241</v>
+        <v>690.4403179644731</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>707.6897014265029</v>
+        <v>695.623004288592</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>634.9294809807731</v>
+        <v>769.6570550317006</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>626.9324436231187</v>
+        <v>780.1460234856705</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>669.6870392767096</v>
+        <v>767.5449518957436</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>667.0120957961387</v>
+        <v>708.8390795102981</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>688.7154420466572</v>
+        <v>618.339000677679</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>740.9672089556665</v>
+        <v>570.517000625955</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>731.6945837245612</v>
+        <v>540.8016815069061</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>744.3125182987558</v>
+        <v>557.510330848757</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>745.5855652443546</v>
+        <v>566.4415684728965</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>728.5808875999749</v>
+        <v>647.7502064243623</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>716.1469357570667</v>
+        <v>706.4986470594334</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>760.0653994688145</v>
+        <v>765.7616145693851</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>758.3217236516333</v>
+        <v>770.4538484979651</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>697.9241263648106</v>
+        <v>696.9135814554903</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>645.6158351387273</v>
+        <v>704.4306659937405</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>621.5869803793623</v>
+        <v>665.6301316101434</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>638.0757517022886</v>
+        <v>650.6105645243139</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>676.347970393266</v>
+        <v>608.8245989123209</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>753.9589870042391</v>
+        <v>608.9268998697577</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>786.3994991255652</v>
+        <v>655.0374607996758</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>823.1543243667403</v>
+        <v>682.1996021534318</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>734.2532215237867</v>
+        <v>713.2803178113249</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>630.3936536372561</v>
+        <v>690.4918623539658</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>604.5059774023542</v>
+        <v>653.416994324914</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>595.7025515542824</v>
+        <v>706.378929568217</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>572.8208436069053</v>
+        <v>687.3692045846838</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>599.2362430953051</v>
+        <v>672.3910846164785</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>653.4339414853747</v>
+        <v>639.7838820715265</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>682.1713998081123</v>
+        <v>670.27378637205</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>758.958708618735</v>
+        <v>698.9175841754189</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>800.870369236435</v>
+        <v>688.1676537049231</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>714.4526735539216</v>
+        <v>684.5998622793417</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>677.4828146522793</v>
+        <v>653.6888624611095</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>639.992850889314</v>
+        <v>635.108134533624</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>610.2857779624884</v>
+        <v>654.7754282470493</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>562.0401766592522</v>
+        <v>676.9788749855365</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>516.2102793924959</v>
+        <v>716.3795028524049</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>519.9446145188062</v>
+        <v>718.5152135611332</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>569.9192735725092</v>
+        <v>726.7578662655296</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>711.2298223892282</v>
+        <v>709.8466801495391</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>794.2583068136742</v>
+        <v>745.270369408459</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>685.5174222544065</v>
+        <v>730.4346641930692</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>608.4041794492947</v>
+        <v>690.3885089670183</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>583.5064790608868</v>
+        <v>727.2206350991013</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>622.8922337703438</v>
+        <v>797.758063426798</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>668.6260451348147</v>
+        <v>807.9040897228538</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>748.8992924859446</v>
+        <v>815.3359127515785</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>818.1756629989678</v>
+        <v>797.3126139022497</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>793.177727024954</v>
+        <v>711.3973882074731</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>609.4501155078262</v>
+        <v>694.0751729074748</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>563.6957073182884</v>
+        <v>722.1209282264454</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>606.5447974912104</v>
+        <v>780.1068414173642</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>597.5978383541758</v>
+        <v>770.3212687175807</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>628.6317123574463</v>
+        <v>742.2968701619652</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>717.3613243821251</v>
+        <v>694.4812100335866</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>819.9900867793417</v>
+        <v>719.2713773299317</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>774.6583021088753</v>
+        <v>722.4713087795891</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>729.0485063078194</v>
+        <v>750.3623058472613</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>643.647959913352</v>
+        <v>813.8366485494259</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>585.3029647182808</v>
+        <v>822.8833713368289</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>601.5547481503063</v>
+        <v>833.2817760791897</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>676.5729254200892</v>
+        <v>830.7895634679738</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>761.3688251712887</v>
+        <v>751.785310584836</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>775.1520974291708</v>
+        <v>803.0038892384823</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>799.1152320223165</v>
+        <v>908.267750533156</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>816.4165842026705</v>
+        <v>916.979040651654</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>722.4679300963857</v>
+        <v>860.224774175407</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>717.7853707866575</v>
+        <v>777.8051990173935</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>689.2483677768553</v>
+        <v>739.3415915755384</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>682.8970965865011</v>
+        <v>687.2045060452194</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>680.7563160107435</v>
+        <v>657.3440252732041</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>666.9850454755135</v>
+        <v>687.4265877668222</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>688.3709255204735</v>
+        <v>661.353337957479</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>684.6241878636476</v>
+        <v>754.2607107555455</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>635.7706417325915</v>
+        <v>837.0069291875666</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>619.0794088176119</v>
+        <v>875.9990426565594</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>587.5389067506944</v>
+        <v>845.4809655833628</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>578.9881878657752</v>
+        <v>842.0264887688518</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>625.6632396595876</v>
+        <v>868.2069122907592</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>636.6440453179791</v>
+        <v>873.5604368790746</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>653.2740566574091</v>
+        <v>793.1317389134733</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>742.0134913180902</v>
+        <v>727.4601174983388</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>752.662489785763</v>
+        <v>765.4667633904353</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>775.9446371583181</v>
+        <v>756.1445892656593</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>773.4044408718717</v>
+        <v>758.839801896471</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>697.6714418444487</v>
+        <v>797.3523104946878</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>693.2938163007236</v>
+        <v>838.6382841251532</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>708.1743650222165</v>
+        <v>831.0626197360023</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>662.5933401862767</v>
+        <v>756.0262269290376</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>605.0051327646315</v>
+        <v>683.4164291537945</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>557.797595398057</v>
+        <v>646.659035280635</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>593.1551478723236</v>
+        <v>671.326746368436</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>572.2211879790109</v>
+        <v>714.4921952248922</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>584.3141976606603</v>
+        <v>729.7191064131709</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>613.8287412966292</v>
+        <v>749.8313058250687</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>632.7695978504551</v>
+        <v>797.8377787467821</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>658.5407864948252</v>
+        <v>780.7050063150598</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>681.7526192197079</v>
+        <v>772.8814815934584</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>689.7658765911387</v>
+        <v>788.3899944920643</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>654.7092378220327</v>
+        <v>748.2906155433966</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>624.7220685773129</v>
+        <v>747.404689709839</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>627.288014492251</v>
+        <v>687.2887721303016</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>647.865722470641</v>
+        <v>574.7684240791386</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>693.1446873119569</v>
+        <v>556.4382408898894</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>739.9940461434653</v>
+        <v>565.5974495969929</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>726.0271262250058</v>
+        <v>609.0671540471533</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>694.3572999318803</v>
+        <v>660.6844754814745</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>626.6084566885581</v>
+        <v>704.0359491420247</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>602.7633578159168</v>
+        <v>750.6083978177571</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>579.989889309104</v>
+        <v>734.3881548252398</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>538.6367309452851</v>
+        <v>742.3167748766275</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>511.5923160681461</v>
+        <v>732.3893746024339</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>476.7317755291458</v>
+        <v>712.6153144112379</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>437.5955185075497</v>
+        <v>761.0923873841671</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>448.5036995703808</v>
+        <v>793.9693035921209</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>438.7475271650771</v>
+        <v>805.661576473824</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>484.5258257764158</v>
+        <v>731.3831099096149</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>540.4891512364145</v>
+        <v>722.9585579786999</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>607.2660758013058</v>
+        <v>703.6296004795872</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>666.0291584713605</v>
+        <v>662.9126506259126</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>663.6161825988438</v>
+        <v>682.5145657482494</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>631.7267656561114</v>
+        <v>722.5026246590005</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>587.4085354013516</v>
+        <v>760.0056287770656</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>554.5609561808078</v>
+        <v>771.5993316118954</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>500.7010239908425</v>
+        <v>769.7504802203525</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>435.7985568435936</v>
+        <v>791.2167265074856</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>388.571336674147</v>
+        <v>797.7964563310707</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>390.51482133371</v>
+        <v>827.8404517733975</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>422.2839517699981</v>
+        <v>823.8995787676515</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>451.0083112749328</v>
+        <v>804.5102020635966</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>447.9252089695933</v>
+        <v>759.6083634176125</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>461.5575018819698</v>
+        <v>714.5455427554737</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>556.1414952150869</v>
+        <v>658.1791183176904</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>581.0898299504856</v>
+        <v>670.9740303311662</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>584.7551874950909</v>
+        <v>666.5725633227169</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>640.025829552286</v>
+        <v>698.737185905685</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>614.4123642918657</v>
+        <v>738.2239933585595</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>564.1146358844082</v>
+        <v>752.3268859535222</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>500.4978149015074</v>
+        <v>772.2152253211618</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>513.6310609707948</v>
+        <v>823.0025657783813</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>535.6217558633034</v>
+        <v>871.2303927808307</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>565.3627045385008</v>
+        <v>822.256604214374</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>529.4470213759439</v>
+        <v>761.9143009703748</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>545.0363824220688</v>
+        <v>747.3101710133392</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>594.2479708135693</v>
+        <v>703.7351118168544</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>619.6337211118532</v>
+        <v>648.3254878929756</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>596.5313224849353</v>
+        <v>599.4321643970295</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>583.9486743132056</v>
+        <v>611.9805469627408</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>653.6405548257562</v>
+        <v>577.6586160525028</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>688.6793866185883</v>
+        <v>600.2350223708106</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>713.87940105555</v>
+        <v>626.2497216506233</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>674.2613452188664</v>
+        <v>668.2374637475448</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>614.3618365265979</v>
+        <v>683.317276206111</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>562.6288190209721</v>
+        <v>698.0237255849318</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>545.2808049461737</v>
+        <v>693.0519801792343</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>577.4188292630811</v>
+        <v>700.5617568707976</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>581.9312984240526</v>
+        <v>744.5533113407521</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>624.4109529848458</v>
+        <v>741.6725428335269</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>667.6814866434313</v>
+        <v>764.3118756865874</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>727.3187123751086</v>
+        <v>766.3133435189025</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>714.1063044854832</v>
+        <v>732.8066092932204</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>661.9593251546974</v>
+        <v>719.9785793095543</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>645.9334914192993</v>
+        <v>692.4797227684962</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>638.5528803697298</v>
+        <v>653.4263519952788</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>646.4298734447311</v>
+        <v>581.2235555303857</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>654.3471775867715</v>
+        <v>556.3572782689334</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>670.3726642625725</v>
+        <v>587.1856033201652</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>658.1249405877827</v>
+        <v>604.9891339748115</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>678.4084451792012</v>
+        <v>615.1593416485355</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>687.6485774252217</v>
+        <v>655.4875229736581</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>768.3534546341377</v>
+        <v>711.3323430266973</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>766.746083415029</v>
+        <v>725.83118744393</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>729.6818836655632</v>
+        <v>802.926934187127</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>698.2764968921344</v>
+        <v>819.8390620022167</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>629.4121115384996</v>
+        <v>769.2399844666511</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>598.5375894182994</v>
+        <v>719.8027954236466</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>611.5503788570322</v>
+        <v>652.5605271425547</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>653.7295502691336</v>
+        <v>627.1569208025767</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>652.3759604523036</v>
+        <v>629.3452321746713</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>651.8679441546453</v>
+        <v>691.0330099209148</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>656.5666551067295</v>
+        <v>700.0594544125534</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>701.5769423294955</v>
+        <v>691.4475762528411</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>704.6062824737191</v>
+        <v>674.8736312399899</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>689.8177956535676</v>
+        <v>671.0267367484164</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>691.682482789588</v>
+        <v>729.0592287035906</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>639.900088821463</v>
+        <v>749.0316598130278</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>644.7757647776768</v>
+        <v>791.1985460881112</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>639.5834186436105</v>
+        <v>774.7153821693757</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>624.9874165684446</v>
+        <v>754.8327511040611</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>601.4169092726718</v>
+        <v>703.9413500195906</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>609.698575992752</v>
+        <v>700.0486382578117</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>609.7481709757346</v>
+        <v>743.7718897850516</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>596.1449645294294</v>
+        <v>719.4460668099794</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>606.6150374591359</v>
+        <v>640.1210073163668</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>606.6161162987385</v>
+        <v>594.1902376260089</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>605.9435228529253</v>
+        <v>571.4443570031733</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>677.2752102917252</v>
+        <v>584.6114728236387</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>775.113410711441</v>
+        <v>623.1152169478662</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>838.7047848854934</v>
+        <v>720.3951879918407</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>781.5150827142077</v>
+        <v>781.8632640288286</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>726.7007828004921</v>
+        <v>829.3667064988028</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>776.6831550167126</v>
+        <v>838.3152283332151</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>726.5992390977658</v>
+        <v>784.0639769075892</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>655.998479324893</v>
+        <v>724.7983299762666</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>644.4330718705942</v>
+        <v>735.7777453233894</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>712.0622539703731</v>
+        <v>726.645070183082</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>733.4756015371795</v>
+        <v>698.1960162631822</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>740.5448360471496</v>
+        <v>639.8496942891825</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>758.5242431601671</v>
+        <v>607.0645087413311</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>713.9028766978015</v>
+        <v>629.8420807654566</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>661.1072326166436</v>
+        <v>705.3472524199549</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>676.5741055239687</v>
+        <v>725.8787296296418</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>668.1671123616866</v>
+        <v>716.7007865124617</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>712.6895504381991</v>
+        <v>699.4449745718043</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>714.665960845366</v>
+        <v>671.4158938596881</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>655.5493325524822</v>
+        <v>681.7175281154846</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>527.0935039446556</v>
+        <v>645.0034429564369</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>531.1319815624813</v>
+        <v>609.9037370085227</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>530.2211065005338</v>
+        <v>642.4379862988872</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>544.4399261045874</v>
+        <v>679.3785319153187</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>545.8608928470881</v>
+        <v>768.0208898614183</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>596.7194667731235</v>
+        <v>760.3984530331616</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>671.8720968932246</v>
+        <v>718.029510090588</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>675.5715336208254</v>
+        <v>739.1249214449829</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>662.4783280558404</v>
+        <v>729.6567289334064</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>712.9495247938564</v>
+        <v>700.3736513287606</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>703.5051760429383</v>
+        <v>689.0864419495131</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>659.8549862190737</v>
+        <v>673.1375868771465</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>681.3686368195704</v>
+        <v>666.8402882300768</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>713.6423640100702</v>
+        <v>669.8999015914069</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>719.7529250297237</v>
+        <v>699.1208112546303</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>674.82341178399</v>
+        <v>673.0337559883424</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>657.767080658914</v>
+        <v>715.1166376888796</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>593.9592568961984</v>
+        <v>675.0441478309597</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>548.3485250953777</v>
+        <v>701.313770390442</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>598.2401590529776</v>
+        <v>739.0817783179386</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>679.1761066818367</v>
+        <v>772.7525169176772</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>696.5863413582269</v>
+        <v>763.6227536440003</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>721.6720202819431</v>
+        <v>743.0441587193002</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>734.1568116172823</v>
+        <v>647.2523839048847</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>728.4869816230923</v>
+        <v>608.4850954296712</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>734.3313320966445</v>
+        <v>611.0456116168166</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>665.8082375568313</v>
+        <v>587.9745316104277</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>616.5927538047811</v>
+        <v>601.1743121295581</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>573.6187899976812</v>
+        <v>659.6784002007894</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>569.7568186778597</v>
+        <v>730.0454557098419</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>591.1996570660847</v>
+        <v>746.9103196817741</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>598.3130498213143</v>
+        <v>751.5420308583316</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>622.5073939880872</v>
+        <v>733.6824250998575</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>607.3733289459824</v>
+        <v>747.6540253096005</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>590.8410737302745</v>
+        <v>720.4951685439482</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>592.7204226266554</v>
+        <v>666.6524827909939</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>619.5650428084605</v>
+        <v>684.2601956739713</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>637.2322508547086</v>
+        <v>636.0112958823834</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>692.8697834262039</v>
+        <v>600.2724727929944</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>678.3763873429223</v>
+        <v>562.3002059136297</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>657.3673693067406</v>
+        <v>570.2171175735202</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>620.3907337516625</v>
+        <v>656.4144681249218</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>557.3425033660158</v>
+        <v>724.7945439481782</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>559.8404314572747</v>
+        <v>770.7677203721346</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>546.2206046672122</v>
+        <v>830.1296471279898</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>517.1970490350191</v>
+        <v>889.6941808501424</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>499.2397084687354</v>
+        <v>862.9975557470857</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>520.5045129517885</v>
+        <v>772.8248120108674</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>589.36387137868</v>
+        <v>734.8274243908008</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>639.5160155659596</v>
+        <v>669.7641843934434</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>635.2946461300348</v>
+        <v>653.6149244140006</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>632.4242069272827</v>
+        <v>651.0550996480333</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>643.7543105970178</v>
+        <v>648.8485720341259</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>632.9352506517125</v>
+        <v>644.5896560923075</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>512.688958671589</v>
+        <v>726.6768924689018</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>486.4166632004867</v>
+        <v>808.5916392548143</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>541.1485022461022</v>
+        <v>798.5854166333297</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>531.2906476709998</v>
+        <v>736.6332840166478</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>529.0144286597922</v>
+        <v>653.185503126565</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>540.045880910327</v>
+        <v>643.8627487236772</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>526.0910043120361</v>
+        <v>676.2420258089605</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>525.8599813154774</v>
+        <v>717.1111045689713</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>471.0945532561936</v>
+        <v>713.5746023534466</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>474.9645438110406</v>
+        <v>740.2226485866095</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>467.5516734857865</v>
+        <v>739.7803824990774</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>488.8032503267823</v>
+        <v>764.0778182092163</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>568.1544580164086</v>
+        <v>747.8468362099875</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>579.323919158071</v>
+        <v>732.7115050053976</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>544.1417203015817</v>
+        <v>707.1505803635887</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>604.9558209989527</v>
+        <v>678.4454312232242</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>699.806424809708</v>
+        <v>684.7856024894554</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>691.4987314503378</v>
+        <v>646.5857283754417</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>646.9730772936941</v>
+        <v>640.2495107172967</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>558.7204411511379</v>
+        <v>684.3313407939036</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>505.5302413806544</v>
+        <v>684.4666550788929</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>467.9812284108493</v>
+        <v>711.4744555656216</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>500.5501273682285</v>
+        <v>715.2549162673836</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>506.2406300252178</v>
+        <v>788.8250011969262</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>516.5601917303206</v>
+        <v>775.2853693322663</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>539.0539927665827</v>
+        <v>762.187080207184</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>548.0609937474128</v>
+        <v>695.7138656699158</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>579.0215566909751</v>
+        <v>643.7756709158293</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>609.8620045598295</v>
+        <v>629.6056592714763</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>624.8685490019739</v>
+        <v>660.6030138233905</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>646.4175183785983</v>
+        <v>657.424933378195</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>556.923143107781</v>
+        <v>706.3824493250763</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>487.6311722602509</v>
+        <v>723.1788608959846</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>501.8875984802662</v>
+        <v>775.6069310362363</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>493.4477031416691</v>
+        <v>754.4367120897277</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>531.6888329767835</v>
+        <v>776.5782495017675</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>566.5664175153324</v>
+        <v>817.8660137037923</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>539.2862008012003</v>
+        <v>870.4241019492542</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>546.1748767314134</v>
+        <v>794.3527198514744</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>594.236531121453</v>
+        <v>761.0234924068777</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>573.5989672904793</v>
+        <v>719.960949602239</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>564.3465750342216</v>
+        <v>710.6269724365006</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>552.0598716326504</v>
+        <v>714.2324076112914</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>562.7964235546301</v>
+        <v>703.27983693943</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>564.5276041078091</v>
+        <v>734.4966697293103</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>560.6945763439626</v>
+        <v>730.3767814066191</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>615.5156366019128</v>
+        <v>714.967057487172</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>632.77268090809</v>
+        <v>732.4932333482366</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>633.7055095508504</v>
+        <v>777.4008505155621</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>602.1251060698205</v>
+        <v>820.5031258174245</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>588.2178848922877</v>
+        <v>811.6109043514825</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>589.5122761716607</v>
+        <v>725.5268938013728</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>621.0496858375336</v>
+        <v>694.0015253277352</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>727.2681428365217</v>
+        <v>668.7946529062287</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>756.3570686871799</v>
+        <v>705.3384197504329</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>738.1999011715834</v>
+        <v>692.7882768497966</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>743.8136855092807</v>
+        <v>698.5045800515763</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>647.2736033688875</v>
+        <v>707.7307763623821</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>602.7812850369401</v>
+        <v>699.2585563511966</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>614.1868270404416</v>
+        <v>721.4192410355622</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>648.1965578839208</v>
+        <v>716.7182963119672</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>630.8675268965089</v>
+        <v>660.7092309652103</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>545.5644095434877</v>
+        <v>619.423871457002</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>560.566134183091</v>
+        <v>656.2797914627936</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>609.9960459130784</v>
+        <v>705.3422033521883</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>674.3405970340746</v>
+        <v>704.4744760937647</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>721.7614306033511</v>
+        <v>766.907671468914</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>707.7056878392796</v>
+        <v>799.2490405093235</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>641.4932964363516</v>
+        <v>765.1399769401905</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>586.9699639275154</v>
+        <v>709.6354011006838</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>576.5357929568609</v>
+        <v>667.4512328090714</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>622.8150724936086</v>
+        <v>622.0288421573059</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>670.602063241688</v>
+        <v>675.0492413455618</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>706.1742110324758</v>
+        <v>664.4047534548463</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>699.6786658796168</v>
+        <v>656.8366457175898</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>641.7038693567179</v>
+        <v>708.702471034826</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>570.5976587157124</v>
+        <v>728.7938276188584</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>578.5573393411028</v>
+        <v>687.364242702472</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>635.4699616825314</v>
+        <v>622.806583211343</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>725.9345644296786</v>
+        <v>648.8187648948838</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>780.5332627917778</v>
+        <v>687.5549201018885</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>721.018977978531</v>
+        <v>702.6131457223528</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>692.8076980362903</v>
+        <v>749.8168290215972</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>722.2207377467953</v>
+        <v>839.3092034745564</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>697.7835860440678</v>
+        <v>821.4619369967977</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>640.8672106820745</v>
+        <v>762.2121910966371</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>599.5310332502868</v>
+        <v>720.2101253885758</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>550.7017176053068</v>
+        <v>654.8361087890271</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>558.1184217789428</v>
+        <v>674.5631508269412</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>566.8058793686441</v>
+        <v>680.3133756739612</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>576.3390786066225</v>
+        <v>749.9741814040135</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>618.1737705845762</v>
+        <v>785.2473014858674</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>626.4300740276667</v>
+        <v>845.0043172478559</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>551.559110853816</v>
+        <v>829.3580828681115</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>498.2722712803138</v>
+        <v>770.0643359035553</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>477.8867024660371</v>
+        <v>676.4755302082222</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>495.9654357005547</v>
+        <v>642.7482311510175</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>522.5779678204958</v>
+        <v>629.4003758582107</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>575.2351237554194</v>
+        <v>651.6751516048771</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>592.309590399509</v>
+        <v>664.7328174933023</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>594.4020593324808</v>
+        <v>701.9263926201234</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>562.865596314964</v>
+        <v>751.8298354301578</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>546.0482789379171</v>
+        <v>756.5682908305007</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>556.0668937748119</v>
+        <v>802.4174904773531</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>562.5923876033312</v>
+        <v>755.2963892539992</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>580.8537123697306</v>
+        <v>764.1717488664881</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>598.9672089542637</v>
+        <v>735.3578298969978</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>619.764315720488</v>
+        <v>703.9736733212294</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>642.5993448239069</v>
+        <v>641.5272426029333</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>605.0921356231242</v>
+        <v>606.7504812990023</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>653.9323902895262</v>
+        <v>602.5833737384119</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>646.7509830468998</v>
+        <v>588.1715018253431</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>683.400862567396</v>
+        <v>637.0365945786602</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>633.6268866822365</v>
+        <v>708.8587109807918</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>575.4231922753661</v>
+        <v>777.8797206178183</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>572.0169690283683</v>
+        <v>701.9644478721148</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>601.4522353592042</v>
+        <v>633.6905398626413</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>574.2530293187542</v>
+        <v>627.8144766877745</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>573.638509202965</v>
+        <v>597.6675492402705</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>589.7292360365896</v>
+        <v>605.6378734191412</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>643.1182309459587</v>
+        <v>613.0860095393587</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>722.9588451514815</v>
+        <v>638.8256689656941</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>778.3328749263774</v>
+        <v>684.7503741201422</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>837.0308168898077</v>
+        <v>756.7564571376124</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>751.2450880939809</v>
+        <v>817.1760301876247</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>591.6253103023337</v>
+        <v>798.8795351307658</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>578.2849181478582</v>
+        <v>731.9791548618468</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>588.7339629835537</v>
+        <v>713.657582388862</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>631.4176022849551</v>
+        <v>732.9053497651898</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>653.5540562683195</v>
+        <v>747.0887373355595</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>646.4877292341384</v>
+        <v>745.6810734126407</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>591.2807164773994</v>
+        <v>740.7430920563343</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>598.5609667347376</v>
+        <v>724.9436675342054</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>597.0420453517704</v>
+        <v>679.6849632092403</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>599.6542378180152</v>
+        <v>640.6691349648668</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>593.4126601108574</v>
+        <v>687.8469442598316</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>625.0250895614613</v>
+        <v>709.4245073575962</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>619.3130504463511</v>
+        <v>628.3567692038332</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>633.5417454640151</v>
+        <v>601.4272043569235</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>655.2620663090352</v>
+        <v>624.4059016781307</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>678.9114452184322</v>
+        <v>687.4315924642929</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>707.7410243286408</v>
+        <v>723.2198944718675</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>717.7644306080992</v>
+        <v>731.1843505581805</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>672.6027571116902</v>
+        <v>720.1323064853682</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>664.3249174520633</v>
+        <v>751.7983270490731</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>660.9378699113222</v>
+        <v>678.6841585198999</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>625.9298318657329</v>
+        <v>654.2408491745846</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>635.7042128196326</v>
+        <v>629.1887111325991</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>619.5715539794264</v>
+        <v>599.377663454959</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>643.8448708817077</v>
+        <v>620.5004877134002</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>682.0345575379747</v>
+        <v>654.4523855882289</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>716.3996669277708</v>
+        <v>624.7086485111026</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>696.8273796657627</v>
+        <v>605.3780696074682</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>599.3751922324577</v>
+        <v>680.1236348488828</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>530.5878169064044</v>
+        <v>714.403358541631</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>579.096059583037</v>
+        <v>756.6322266917496</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>662.2057091877309</v>
+        <v>770.7094330434643</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>705.3235423918522</v>
+        <v>760.9378316992661</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>717.7302493342381</v>
+        <v>680.9094825751458</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>701.2896296609483</v>
+        <v>632.7313692075336</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>734.4023331291964</v>
+        <v>681.7074729187311</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>778.1900524465755</v>
+        <v>722.3636542054805</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>800.5014931065375</v>
+        <v>733.5695285303245</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>747.2972176833537</v>
+        <v>697.8235952354339</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>712.232633210192</v>
+        <v>762.2540021958457</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>653.5411945787928</v>
+        <v>814.5111857011216</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>632.9715066949575</v>
+        <v>804.4129637527817</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>575.6811413350533</v>
+        <v>817.8400059036335</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>503.3810509908108</v>
+        <v>773.3470733029435</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>499.7658741938267</v>
+        <v>746.276142746467</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>529.5950756416801</v>
+        <v>770.6284288594247</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>557.1353025086978</v>
+        <v>723.2085383650997</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>582.1763346130524</v>
+        <v>741.6869086433735</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>622.4667757255702</v>
+        <v>750.9779409796238</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>693.6654804259206</v>
+        <v>725.5875423943507</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>719.3760657398229</v>
+        <v>680.0599477447804</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>754.4157525468336</v>
+        <v>671.8794922919074</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>668.4627106117773</v>
+        <v>687.5102387932088</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>617.2036845816251</v>
+        <v>703.6665339230694</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>583.3566999461937</v>
+        <v>679.4937812287571</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>563.2050765998429</v>
+        <v>722.2583178271975</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>538.0616295523168</v>
+        <v>724.6747790516679</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>557.0531480924501</v>
+        <v>763.8167516347494</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>598.3143553132777</v>
+        <v>682.7996629307904</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>664.757597547009</v>
+        <v>673.218656415429</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>730.105214959849</v>
+        <v>687.2828505831308</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>724.9942202357147</v>
+        <v>702.1078526809106</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>613.700439958734</v>
+        <v>699.4736768098164</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>541.3833836183812</v>
+        <v>702.3927194958333</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>474.4997904616639</v>
+        <v>697.2187993879402</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>465.1494167118244</v>
+        <v>717.0987190894493</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>448.0623385722993</v>
+        <v>721.9701293586809</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>455.0733603375647</v>
+        <v>686.5743839327365</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>525.8447465869835</v>
+        <v>656.5879724203114</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>652.023621391038</v>
+        <v>677.456858227913</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>723.9959205832065</v>
+        <v>732.0374798667899</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>787.5013021209725</v>
+        <v>734.8451400693534</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>897.5031739844894</v>
+        <v>795.7355936593444</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>837.6709633213864</v>
+        <v>788.8111752184841</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>852.1251781544379</v>
+        <v>720.3631347973101</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>775.584487139497</v>
+        <v>645.4042048005135</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>640.0620463780911</v>
+        <v>599.0727662618269</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>594.7505898376448</v>
+        <v>586.7453479767164</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>598.7566942863509</v>
+        <v>585.7984849018294</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>603.0581153529511</v>
+        <v>638.9710112239868</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>534.7618187556122</v>
+        <v>693.9027984040536</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>531.7247061447006</v>
+        <v>719.8817977692329</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>564.9306789039201</v>
+        <v>716.3735448014563</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>630.4503246198578</v>
+        <v>730.8213776880166</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>669.0842449419847</v>
+        <v>695.2483886444725</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>662.4528605291289</v>
+        <v>666.5272722982536</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>652.9156313582121</v>
+        <v>624.3740889722744</v>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>626.0558204156155</v>
+        <v>614.5729985174739</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>594.0533335646592</v>
+        <v>670.8027059997335</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>558.2208360825689</v>
+        <v>717.02347569925</v>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>500.7152257516054</v>
+        <v>743.842980219199</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>507.2910824020482</v>
+        <v>752.9906846725112</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>517.3142378814646</v>
+        <v>759.0017410734617</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>509.5596325959946</v>
+        <v>769.9787118269228</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>573.6808541670939</v>
+        <v>789.1696145254627</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>653.0153042758116</v>
+        <v>777.277366966814</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>756.9162684263233</v>
+        <v>724.7833714618537</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>759.3179397426866</v>
+        <v>716.8977053021308</v>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>755.3303911447529</v>
+        <v>739.3865122068632</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>711.8162010988272</v>
+        <v>790.5885813826785</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>636.8037361117445</v>
+        <v>841.4398789142865</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>524.4104917246091</v>
+        <v>901.6321734237067</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>454.3820112333492</v>
+        <v>855.3724916341707</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>427.949292107769</v>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="n">
-        <v>456.8363963642241</v>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="n">
-        <v>516.547638003658</v>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="n">
-        <v>606.0742715167748</v>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="n">
-        <v>650.0890471660909</v>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="n">
-        <v>668.0213015866912</v>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="n">
-        <v>723.3155412880592</v>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="n">
-        <v>715.5523530519758</v>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="n">
-        <v>654.0529291182793</v>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="n">
-        <v>568.4438209166274</v>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="n">
-        <v>537.0138417699195</v>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="n">
-        <v>585.4821983294869</v>
-      </c>
-    </row>
-    <row r="633">
-      <c r="A633" t="n">
-        <v>613.469140064467</v>
-      </c>
-    </row>
-    <row r="634">
-      <c r="A634" t="n">
-        <v>630.8487649424706</v>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="n">
-        <v>633.8982088623197</v>
-      </c>
-    </row>
-    <row r="636">
-      <c r="A636" t="n">
-        <v>629.7367587126246</v>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="n">
-        <v>602.3960771429984</v>
-      </c>
-    </row>
-    <row r="638">
-      <c r="A638" t="n">
-        <v>631.1199081975474</v>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="n">
-        <v>617.3535886410946</v>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="n">
-        <v>592.8776147288772</v>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="n">
-        <v>619.9941050365396</v>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="n">
-        <v>617.509094063621</v>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="n">
-        <v>594.3930910916606</v>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="n">
-        <v>527.3990838427949</v>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="n">
-        <v>487.708963188993</v>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="n">
-        <v>479.6128241029578</v>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="n">
-        <v>488.6631542300961</v>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="n">
-        <v>537.6846335113896</v>
-      </c>
-    </row>
-    <row r="649">
-      <c r="A649" t="n">
-        <v>593.7945735631729</v>
-      </c>
-    </row>
-    <row r="650">
-      <c r="A650" t="n">
-        <v>643.0653835814155</v>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="n">
-        <v>604.3653870261778</v>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="n">
-        <v>571.9913879195815</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="n">
-        <v>586.3383412895473</v>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="n">
-        <v>594.0249133938096</v>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="n">
-        <v>595.3372619254651</v>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="n">
-        <v>609.8636259148975</v>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="n">
-        <v>573.1329174689677</v>
-      </c>
-    </row>
-    <row r="658">
-      <c r="A658" t="n">
-        <v>545.2483028702204</v>
-      </c>
-    </row>
-    <row r="659">
-      <c r="A659" t="n">
-        <v>535.1568150706498</v>
-      </c>
-    </row>
-    <row r="660">
-      <c r="A660" t="n">
-        <v>554.6625969113848</v>
-      </c>
-    </row>
-    <row r="661">
-      <c r="A661" t="n">
-        <v>604.3563629450546</v>
-      </c>
-    </row>
-    <row r="662">
-      <c r="A662" t="n">
-        <v>635.0230940439587</v>
-      </c>
-    </row>
-    <row r="663">
-      <c r="A663" t="n">
-        <v>645.1159252973753</v>
-      </c>
-    </row>
-    <row r="664">
-      <c r="A664" t="n">
-        <v>666.6419237216132</v>
-      </c>
-    </row>
-    <row r="665">
-      <c r="A665" t="n">
-        <v>628.3963076857049</v>
-      </c>
-    </row>
-    <row r="666">
-      <c r="A666" t="n">
-        <v>608.2198601433788</v>
-      </c>
-    </row>
-    <row r="667">
-      <c r="A667" t="n">
-        <v>648.0676732094253</v>
-      </c>
-    </row>
-    <row r="668">
-      <c r="A668" t="n">
-        <v>606.6116451412995</v>
-      </c>
-    </row>
-    <row r="669">
-      <c r="A669" t="n">
-        <v>594.2092345019887</v>
-      </c>
-    </row>
-    <row r="670">
-      <c r="A670" t="n">
-        <v>637.4977391732273</v>
-      </c>
-    </row>
-    <row r="671">
-      <c r="A671" t="n">
-        <v>649.6808434725949</v>
-      </c>
-    </row>
-    <row r="672">
-      <c r="A672" t="n">
-        <v>655.276565100678</v>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="n">
-        <v>680.6672823568647</v>
-      </c>
-    </row>
-    <row r="674">
-      <c r="A674" t="n">
-        <v>621.8141659649632</v>
-      </c>
-    </row>
-    <row r="675">
-      <c r="A675" t="n">
-        <v>593.285754277133</v>
-      </c>
-    </row>
-    <row r="676">
-      <c r="A676" t="n">
-        <v>623.5026202191989</v>
-      </c>
-    </row>
-    <row r="677">
-      <c r="A677" t="n">
-        <v>603.0040798962091</v>
-      </c>
-    </row>
-    <row r="678">
-      <c r="A678" t="n">
-        <v>602.7772363163422</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="n">
-        <v>652.3709717782822</v>
-      </c>
-    </row>
-    <row r="680">
-      <c r="A680" t="n">
-        <v>615.7848120740255</v>
-      </c>
-    </row>
-    <row r="681">
-      <c r="A681" t="n">
-        <v>638.1792579723538</v>
-      </c>
-    </row>
-    <row r="682">
-      <c r="A682" t="n">
-        <v>690.6879938554198</v>
-      </c>
-    </row>
-    <row r="683">
-      <c r="A683" t="n">
-        <v>679.3401383681612</v>
-      </c>
-    </row>
-    <row r="684">
-      <c r="A684" t="n">
-        <v>693.8476031714345</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="n">
-        <v>626.8686446188667</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="A686" t="n">
-        <v>578.8444961882533</v>
-      </c>
-    </row>
-    <row r="687">
-      <c r="A687" t="n">
-        <v>593.2370442638444</v>
-      </c>
-    </row>
-    <row r="688">
-      <c r="A688" t="n">
-        <v>625.3202616134104</v>
-      </c>
-    </row>
-    <row r="689">
-      <c r="A689" t="n">
-        <v>672.1946047975393</v>
-      </c>
-    </row>
-    <row r="690">
-      <c r="A690" t="n">
-        <v>708.0189385206381</v>
-      </c>
-    </row>
-    <row r="691">
-      <c r="A691" t="n">
-        <v>756.5188731887247</v>
-      </c>
-    </row>
-    <row r="692">
-      <c r="A692" t="n">
-        <v>781.8954548662305</v>
-      </c>
-    </row>
-    <row r="693">
-      <c r="A693" t="n">
-        <v>849.6043308122125</v>
-      </c>
-    </row>
-    <row r="694">
-      <c r="A694" t="n">
-        <v>700.7552625159406</v>
-      </c>
-    </row>
-    <row r="695">
-      <c r="A695" t="n">
-        <v>595.6746733040177</v>
-      </c>
-    </row>
-    <row r="696">
-      <c r="A696" t="n">
-        <v>552.4063877292065</v>
-      </c>
-    </row>
-    <row r="697">
-      <c r="A697" t="n">
-        <v>580.1422720292635</v>
+        <v>876.5324670692962</v>
       </c>
     </row>
   </sheetData>
